--- a/src/scraping/data/initial_url.xlsx
+++ b/src/scraping/data/initial_url.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ipsosgroup-my.sharepoint.com/personal/yuding_duan_ipsos_com/Documents/3. self_projects/competitor_product_search/src/scraping/data/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="113" documentId="11_F25DC773A252ABDACC10487A315C701A5ADE58E8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9BE1BA3D-D862-4C04-86D3-3F1865630036}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -18,12 +24,129 @@
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="32">
+  <si>
+    <t>url</t>
+  </si>
+  <si>
+    <t>host</t>
+  </si>
+  <si>
+    <t>https://www.tesco.com/groceries/en-GB/products/276797313</t>
+  </si>
+  <si>
+    <t>https://www.tesco.com/groceries/en-GB/products/312841117</t>
+  </si>
+  <si>
+    <t>https://www.tesco.com/shop/en-GB/products/326405420</t>
+  </si>
+  <si>
+    <t>https://www.tesco.com/shop/en-GB/products/325602141</t>
+  </si>
+  <si>
+    <t>https://www.tesco.com/shop/en-GB/products/297568023</t>
+  </si>
+  <si>
+    <t>https://www.tesco.com/shop/en-GB/products/303350818</t>
+  </si>
+  <si>
+    <t>https://www.tesco.com/shop/en-GB/products/325296757</t>
+  </si>
+  <si>
+    <t>https://www.tesco.com/shop/en-GB/products/320797857</t>
+  </si>
+  <si>
+    <t>label</t>
+  </si>
+  <si>
+    <t>normal</t>
+  </si>
+  <si>
+    <t>discount</t>
+  </si>
+  <si>
+    <t>error</t>
+  </si>
+  <si>
+    <t>unavailable</t>
+  </si>
+  <si>
+    <t>tesco.com</t>
+  </si>
+  <si>
+    <t>https://www.argos.co.uk/product/8189978</t>
+  </si>
+  <si>
+    <t>argos.co.uk</t>
+  </si>
+  <si>
+    <t>https://www.argos.co.uk/product/8747437</t>
+  </si>
+  <si>
+    <t>https://www.argos.co.uk/product/7726844</t>
+  </si>
+  <si>
+    <t>https://www.argos.co.uk/product/8343893</t>
+  </si>
+  <si>
+    <t>https://www.argos.co.uk/product/7123351</t>
+  </si>
+  <si>
+    <t>https://www.argos.co.uk/browse/garden-and-diy/plant-and-lawn-care/grass-seed-and-feed/c:1040915</t>
+  </si>
+  <si>
+    <t>https://www.amazon.co.uk/Kids-Bike-Handwoven-Streamers-Detachable/dp/B0B1QJ42KN</t>
+  </si>
+  <si>
+    <t>amazon.co.uk</t>
+  </si>
+  <si>
+    <t>https://www.amazon.co.uk/MIETONG-Pair-Bicycle-Handlebar-Streamers/dp/B0DYHJCM5Q</t>
+  </si>
+  <si>
+    <t>https://www.amazon.co.uk/Included-Accessories-Propellers-Motorcycle-Decoration/dp/B0DY727FDV</t>
+  </si>
+  <si>
+    <t>https://www.amazon.co.uk/Samsung-Features-Speakers-Extended-Warranty/dp/B0FQDX2XGZ</t>
+  </si>
+  <si>
+    <t>https://www.amazon.co.uk/DWVO-Storage-Sandbags-Waterproof-Weddings/dp/B0GT4SPPSY</t>
+  </si>
+  <si>
+    <t>https://www.amazon.co.uk/BEEWAY-Parasol-Waterproof-Cantilever-Umbrella/dp/B0DQTSQ42Z</t>
+  </si>
+  <si>
+    <t>https://www.argos.co.uk/product/4490582</t>
+  </si>
+  <si>
+    <t>https://www.argos.co.uk/product/3284476</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -46,13 +169,17 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -66,6 +193,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -330,10 +461,292 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:C23"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="14.21875" customWidth="1"/>
+    <col min="3" max="3" width="11.109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>13</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C6" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C7" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>13</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C8" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>14</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>11</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C10" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>12</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C11" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>11</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C12" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>11</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C13" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>12</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C14" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>11</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C15" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>13</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C16" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>13</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C17" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>12</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C18" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>11</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C19" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>12</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C20" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>12</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C21" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>11</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C22" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>12</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C23" t="s">
+        <v>24</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="B6" r:id="rId1" xr:uid="{D6C08F61-3568-4CA3-9CF6-78D6A0F2B4B6}"/>
+    <hyperlink ref="B4" r:id="rId2" xr:uid="{020150A2-A429-47E6-8DDF-195404F838CD}"/>
+    <hyperlink ref="B5" r:id="rId3" xr:uid="{0B6A073D-EC83-4343-864A-63A4870BED87}"/>
+    <hyperlink ref="B7" r:id="rId4" xr:uid="{142478F9-6760-4981-A2D1-A6E9AFF44E50}"/>
+    <hyperlink ref="B8" r:id="rId5" xr:uid="{1DA2DCDF-E91D-4BD0-92D7-9E4D51A10800}"/>
+    <hyperlink ref="B15" r:id="rId6" xr:uid="{1FDAC294-0CD9-48FC-B956-E42B74C8AC8F}"/>
+    <hyperlink ref="B16" r:id="rId7" xr:uid="{62EBD053-CAB5-4318-AB27-A6C9A064E414}"/>
+    <hyperlink ref="B2" r:id="rId8" xr:uid="{088A3374-DC49-4FF4-8803-48AE6DB6B735}"/>
+    <hyperlink ref="B3" r:id="rId9" xr:uid="{9C8AFB8D-75E9-40B2-B481-4FC988DD364F}"/>
+    <hyperlink ref="B9" r:id="rId10" xr:uid="{2E2BC055-4BF7-4440-B7CF-6B78DDCAC401}"/>
+    <hyperlink ref="B10" r:id="rId11" xr:uid="{61AC43EE-B630-46D0-A894-576D2FEF9B57}"/>
+    <hyperlink ref="B12" r:id="rId12" xr:uid="{331DDCD4-7758-4E84-8865-61DBA6388B25}"/>
+    <hyperlink ref="B13" r:id="rId13" xr:uid="{0AB22088-E64F-4AEE-8EB1-33148248849C}"/>
+    <hyperlink ref="B14" r:id="rId14" xr:uid="{0A40D1DD-6436-4EF9-89C4-06A64670EAFF}"/>
+    <hyperlink ref="B11" r:id="rId15" xr:uid="{AAF2C0D4-EA52-4A31-AAD1-4C573B52EE4F}"/>
+    <hyperlink ref="B17" r:id="rId16" xr:uid="{0C3D4F24-AA28-4943-AED1-A70DC828744B}"/>
+    <hyperlink ref="B18" r:id="rId17" xr:uid="{486A4D85-47DF-4F58-B1A5-2FB1C6708E8E}"/>
+    <hyperlink ref="B19" r:id="rId18" xr:uid="{CC412CCC-A2FF-45FA-B3CC-AC66ABC5697B}"/>
+    <hyperlink ref="B20" r:id="rId19" xr:uid="{EE5AD17D-B48F-4240-A762-93E7634DE534}"/>
+    <hyperlink ref="B21" r:id="rId20" xr:uid="{6DD1C4E9-4CB0-4F5E-ABEB-4B7F15B1C7CC}"/>
+    <hyperlink ref="B22" r:id="rId21" xr:uid="{F7015BDC-B0AA-4A77-A773-FF6AB1D03A10}"/>
+    <hyperlink ref="B23" r:id="rId22" xr:uid="{8DFAB6B6-1FD6-42CC-8F50-507F2EEBA55D}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>